--- a/data/roles_areas.xlsx
+++ b/data/roles_areas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Inventario\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F58EBE-1CCE-4B81-BFCA-60B703E8BD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0C1D12-9498-435B-9D13-65DE65B05CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F2D9A4D-AB14-4069-820F-8029A79ED844}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8F2D9A4D-AB14-4069-820F-8029A79ED844}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5349,12 +5349,12 @@
   <dimension ref="A1:F1537"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/data/roles_areas.xlsx
+++ b/data/roles_areas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Inventario\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C811B3-CC69-4DB6-97CB-518BC36F7D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17885699-5A4D-4793-BC03-F171F39DD063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8F2D9A4D-AB14-4069-820F-8029A79ED844}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15288" uniqueCount="1631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15289" uniqueCount="1631">
   <si>
     <t>Nombre</t>
   </si>
@@ -41267,6 +41267,9 @@
       <c r="B12" t="s">
         <v>33</v>
       </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -41853,9 +41856,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F16" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F16" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>1617</v>
@@ -42178,9 +42181,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F29" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F29" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>1617</v>
@@ -42453,9 +42456,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F40" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F40" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>1617</v>
@@ -42628,9 +42631,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F47" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F47" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>1617</v>
@@ -42953,9 +42956,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F60" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F60" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>1617</v>
@@ -43303,9 +43306,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F74" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F74" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>1617</v>
@@ -43953,9 +43956,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F100" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F100" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>1617</v>
@@ -44603,9 +44606,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F126" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F126" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>1617</v>
@@ -45978,9 +45981,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F181" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F181" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>1615</v>
@@ -46328,9 +46331,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F195" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F195" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>1617</v>
@@ -47353,9 +47356,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F236" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F236" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G236" s="3" t="s">
         <v>1614</v>
@@ -48628,9 +48631,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F287" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F287" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G287" s="3" t="s">
         <v>1615</v>
@@ -49103,9 +49106,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F306" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F306" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G306" s="3" t="s">
         <v>1615</v>
@@ -49928,9 +49931,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F339" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F339" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G339" s="3" t="s">
         <v>1617</v>
@@ -50053,9 +50056,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F344" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F344" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G344" s="3" t="s">
         <v>1617</v>
@@ -50228,9 +50231,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F351" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F351" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G351" s="3" t="s">
         <v>1614</v>
@@ -50378,9 +50381,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F357" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F357" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G357" s="3" t="s">
         <v>1617</v>
@@ -50753,9 +50756,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F372" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F372" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G372" s="3" t="s">
         <v>1614</v>
@@ -51128,9 +51131,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F387" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F387" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G387" s="3" t="s">
         <v>1614</v>
@@ -51678,9 +51681,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F409" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F409" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G409" s="3" t="s">
         <v>1615</v>
@@ -51778,9 +51781,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F413" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F413" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G413" s="3" t="s">
         <v>1617</v>
@@ -51953,9 +51956,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F420" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F420" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>1617</v>
@@ -53878,9 +53881,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F497" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F497" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G497" s="3" t="s">
         <v>1616</v>
@@ -54228,9 +54231,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F511" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F511" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G511" s="3" t="s">
         <v>1614</v>
@@ -54903,9 +54906,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F538" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F538" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G538" s="3" t="s">
         <v>1617</v>
@@ -55378,9 +55381,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F557" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F557" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G557" s="3" t="s">
         <v>1617</v>
@@ -55403,9 +55406,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F558" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F558" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G558" s="3" t="s">
         <v>1617</v>
@@ -56903,9 +56906,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F618" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F618" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G618" s="3" t="s">
         <v>1614</v>
@@ -57278,9 +57281,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F633" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F633" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G633" s="3" t="s">
         <v>1617</v>
@@ -57903,9 +57906,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F658" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F658" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G658" s="3" t="s">
         <v>1617</v>
@@ -57928,9 +57931,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F659" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F659" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G659" s="3" t="s">
         <v>1617</v>
@@ -57978,9 +57981,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F661" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F661" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G661" s="3" t="s">
         <v>1617</v>
@@ -58128,9 +58131,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F667" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F667" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G667" s="3" t="s">
         <v>1617</v>
@@ -58178,9 +58181,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F669" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F669" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G669" s="3" t="s">
         <v>1615</v>
@@ -58478,9 +58481,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F681" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F681" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G681" s="3" t="s">
         <v>1616</v>
@@ -58603,9 +58606,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F686" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F686" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G686" s="3" t="s">
         <v>1615</v>
@@ -59003,9 +59006,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F702" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F702" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G702" s="3" t="s">
         <v>1617</v>
@@ -59128,9 +59131,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F707" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F707" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G707" s="3" t="s">
         <v>1615</v>
@@ -60228,9 +60231,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F751" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F751" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G751" s="3" t="s">
         <v>1617</v>
@@ -60328,9 +60331,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F755" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F755" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G755" s="3" t="s">
         <v>1615</v>
@@ -61303,9 +61306,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F794" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F794" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G794" s="3" t="s">
         <v>1617</v>
@@ -61753,9 +61756,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F812" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F812" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G812" s="3" t="s">
         <v>1617</v>
@@ -62653,9 +62656,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F848" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F848" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G848" s="3" t="s">
         <v>1617</v>
@@ -63628,9 +63631,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F887" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F887" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G887" s="3" t="s">
         <v>1617</v>
@@ -64128,9 +64131,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F907" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F907" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G907" s="3" t="s">
         <v>1617</v>
@@ -65778,9 +65781,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F973" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F973" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G973" s="3" t="s">
         <v>1615</v>
@@ -66878,9 +66881,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1017" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1017" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1017" s="3" t="s">
         <v>1616</v>
@@ -67053,9 +67056,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1024" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1024" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1024" s="3" t="s">
         <v>1617</v>
@@ -67653,9 +67656,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1048" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1048" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1048" s="3" t="s">
         <v>1615</v>
@@ -67878,9 +67881,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1057" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1057" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1057" s="3" t="s">
         <v>1615</v>
@@ -68278,9 +68281,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1073" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1073" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1073" s="3" t="s">
         <v>1615</v>
@@ -69853,9 +69856,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1136" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1136" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1136" s="3" t="s">
         <v>1616</v>
@@ -70278,9 +70281,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1153" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1153" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1153" s="3" t="s">
         <v>1615</v>
@@ -70378,9 +70381,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1157" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1157" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1157" s="3" t="s">
         <v>1615</v>
@@ -70678,9 +70681,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1169" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1169" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1169" s="3" t="s">
         <v>1615</v>
@@ -71353,9 +71356,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1196" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1196" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1196" s="3" t="s">
         <v>1615</v>
@@ -72353,9 +72356,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1236" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1236" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1236" s="3" t="s">
         <v>1615</v>
@@ -73978,9 +73981,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1301" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1301" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1301" s="3" t="s">
         <v>1615</v>
@@ -74328,9 +74331,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1315" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1315" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1315" s="3" t="s">
         <v>1615</v>
@@ -76503,9 +76506,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1402" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1402" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1402" s="3" t="s">
         <v>1615</v>
@@ -77203,9 +77206,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1430" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1430" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1430" s="3" t="s">
         <v>1616</v>
@@ -78003,9 +78006,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1462" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1462" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1462" s="3" t="s">
         <v>1615</v>
@@ -78028,9 +78031,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1463" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1463" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1463" s="3" t="s">
         <v>1615</v>
@@ -78103,9 +78106,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1466" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1466" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1466" s="3" t="s">
         <v>1615</v>
@@ -78878,9 +78881,9 @@
         <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]],Table1[Location],Table1[Oracle Location],0,0)</f>
         <v>MONDA</v>
       </c>
-      <c r="F1497" s="3">
-        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
-        <v>0</v>
+      <c r="F1497" s="3" t="str">
+        <f>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</f>
+        <v>MONDA</v>
       </c>
       <c r="G1497" s="3" t="s">
         <v>1615</v>

--- a/data/roles_areas.xlsx
+++ b/data/roles_areas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Inventario\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17885699-5A4D-4793-BC03-F171F39DD063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA9A64B-DE22-47F4-92FB-2D610FA33840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8F2D9A4D-AB14-4069-820F-8029A79ED844}"/>
   </bookViews>
@@ -41449,8 +41449,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/roles_areas.xlsx
+++ b/data/roles_areas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Inventario\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA9A64B-DE22-47F4-92FB-2D610FA33840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D89E04-6C5F-4A01-BA1A-828E35AA582E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8F2D9A4D-AB14-4069-820F-8029A79ED844}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F2D9A4D-AB14-4069-820F-8029A79ED844}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15289" uniqueCount="1631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15354" uniqueCount="1631">
   <si>
     <t>Nombre</t>
   </si>
@@ -6096,8 +6096,8 @@
       <c r="E16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="3">
-        <v>0</v>
+      <c r="F16" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>1617</v>
@@ -6395,8 +6395,8 @@
       <c r="E29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
+      <c r="F29" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>1617</v>
@@ -6648,8 +6648,8 @@
       <c r="E40" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="3">
-        <v>0</v>
+      <c r="F40" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>1617</v>
@@ -6809,8 +6809,8 @@
       <c r="E47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="F47" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>1617</v>
@@ -7108,8 +7108,8 @@
       <c r="E60" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F60" s="3">
-        <v>0</v>
+      <c r="F60" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>1617</v>
@@ -7430,8 +7430,8 @@
       <c r="E74" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F74" s="3">
-        <v>0</v>
+      <c r="F74" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>1617</v>
@@ -8028,8 +8028,8 @@
       <c r="E100" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="F100" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>1617</v>
@@ -8626,8 +8626,8 @@
       <c r="E126" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F126" s="3">
-        <v>0</v>
+      <c r="F126" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>1617</v>
@@ -9891,8 +9891,8 @@
       <c r="E181" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F181" s="3">
-        <v>0</v>
+      <c r="F181" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>1615</v>
@@ -10213,8 +10213,8 @@
       <c r="E195" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F195" s="3">
-        <v>0</v>
+      <c r="F195" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>1617</v>
@@ -11156,8 +11156,8 @@
       <c r="E236" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F236" s="3">
-        <v>0</v>
+      <c r="F236" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G236" s="3" t="s">
         <v>1614</v>
@@ -12329,8 +12329,8 @@
       <c r="E287" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F287" s="3">
-        <v>0</v>
+      <c r="F287" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G287" s="3" t="s">
         <v>1615</v>
@@ -12766,8 +12766,8 @@
       <c r="E306" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F306" s="3">
-        <v>0</v>
+      <c r="F306" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G306" s="3" t="s">
         <v>1615</v>
@@ -13525,8 +13525,8 @@
       <c r="E339" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F339" s="3">
-        <v>0</v>
+      <c r="F339" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G339" s="3" t="s">
         <v>1617</v>
@@ -13640,8 +13640,8 @@
       <c r="E344" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F344" s="3">
-        <v>0</v>
+      <c r="F344" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G344" s="3" t="s">
         <v>1617</v>
@@ -13801,8 +13801,8 @@
       <c r="E351" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F351" s="3">
-        <v>0</v>
+      <c r="F351" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G351" s="3" t="s">
         <v>1614</v>
@@ -13939,8 +13939,8 @@
       <c r="E357" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F357" s="3">
-        <v>0</v>
+      <c r="F357" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G357" s="3" t="s">
         <v>1617</v>
@@ -14284,8 +14284,8 @@
       <c r="E372" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F372" s="3">
-        <v>0</v>
+      <c r="F372" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G372" s="3" t="s">
         <v>1614</v>
@@ -14629,8 +14629,8 @@
       <c r="E387" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F387" s="3">
-        <v>0</v>
+      <c r="F387" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G387" s="3" t="s">
         <v>1614</v>
@@ -15135,8 +15135,8 @@
       <c r="E409" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F409" s="3">
-        <v>0</v>
+      <c r="F409" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G409" s="3" t="s">
         <v>1615</v>
@@ -15227,8 +15227,8 @@
       <c r="E413" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F413" s="3">
-        <v>0</v>
+      <c r="F413" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G413" s="3" t="s">
         <v>1617</v>
@@ -15388,8 +15388,8 @@
       <c r="E420" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F420" s="3">
-        <v>0</v>
+      <c r="F420" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>1617</v>
@@ -17159,8 +17159,8 @@
       <c r="E497" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F497" s="3">
-        <v>0</v>
+      <c r="F497" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G497" s="3" t="s">
         <v>1616</v>
@@ -17481,8 +17481,8 @@
       <c r="E511" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F511" s="3">
-        <v>0</v>
+      <c r="F511" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G511" s="3" t="s">
         <v>1614</v>
@@ -18102,8 +18102,8 @@
       <c r="E538" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F538" s="3">
-        <v>0</v>
+      <c r="F538" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G538" s="3" t="s">
         <v>1617</v>
@@ -18539,8 +18539,8 @@
       <c r="E557" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F557" s="3">
-        <v>0</v>
+      <c r="F557" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G557" s="3" t="s">
         <v>1617</v>
@@ -18562,8 +18562,8 @@
       <c r="E558" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F558" s="3">
-        <v>0</v>
+      <c r="F558" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G558" s="3" t="s">
         <v>1617</v>
@@ -19942,8 +19942,8 @@
       <c r="E618" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F618" s="3">
-        <v>0</v>
+      <c r="F618" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G618" s="3" t="s">
         <v>1614</v>
@@ -20287,8 +20287,8 @@
       <c r="E633" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F633" s="3">
-        <v>0</v>
+      <c r="F633" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G633" s="3" t="s">
         <v>1617</v>
@@ -20862,8 +20862,8 @@
       <c r="E658" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F658" s="3">
-        <v>0</v>
+      <c r="F658" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G658" s="3" t="s">
         <v>1617</v>
@@ -20885,8 +20885,8 @@
       <c r="E659" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F659" s="3">
-        <v>0</v>
+      <c r="F659" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G659" s="3" t="s">
         <v>1617</v>
@@ -20931,8 +20931,8 @@
       <c r="E661" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F661" s="3">
-        <v>0</v>
+      <c r="F661" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G661" s="3" t="s">
         <v>1617</v>
@@ -21069,8 +21069,8 @@
       <c r="E667" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F667" s="3">
-        <v>0</v>
+      <c r="F667" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G667" s="3" t="s">
         <v>1617</v>
@@ -21115,8 +21115,8 @@
       <c r="E669" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F669" s="3">
-        <v>0</v>
+      <c r="F669" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G669" s="3" t="s">
         <v>1615</v>
@@ -21391,8 +21391,8 @@
       <c r="E681" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F681" s="3">
-        <v>0</v>
+      <c r="F681" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G681" s="3" t="s">
         <v>1616</v>
@@ -21506,8 +21506,8 @@
       <c r="E686" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F686" s="3">
-        <v>0</v>
+      <c r="F686" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G686" s="3" t="s">
         <v>1615</v>
@@ -21874,8 +21874,8 @@
       <c r="E702" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F702" s="3">
-        <v>0</v>
+      <c r="F702" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G702" s="3" t="s">
         <v>1617</v>
@@ -21989,8 +21989,8 @@
       <c r="E707" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F707" s="3">
-        <v>0</v>
+      <c r="F707" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G707" s="3" t="s">
         <v>1615</v>
@@ -23001,8 +23001,8 @@
       <c r="E751" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F751" s="3">
-        <v>0</v>
+      <c r="F751" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G751" s="3" t="s">
         <v>1617</v>
@@ -23093,8 +23093,8 @@
       <c r="E755" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F755" s="3">
-        <v>0</v>
+      <c r="F755" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G755" s="3" t="s">
         <v>1615</v>
@@ -23990,8 +23990,8 @@
       <c r="E794" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F794" s="3">
-        <v>0</v>
+      <c r="F794" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G794" s="3" t="s">
         <v>1617</v>
@@ -24404,8 +24404,8 @@
       <c r="E812" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F812" s="3">
-        <v>0</v>
+      <c r="F812" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G812" s="3" t="s">
         <v>1617</v>
@@ -25232,8 +25232,8 @@
       <c r="E848" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F848" s="3">
-        <v>0</v>
+      <c r="F848" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G848" s="3" t="s">
         <v>1617</v>
@@ -26129,8 +26129,8 @@
       <c r="E887" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F887" s="3">
-        <v>0</v>
+      <c r="F887" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G887" s="3" t="s">
         <v>1617</v>
@@ -26589,8 +26589,8 @@
       <c r="E907" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F907" s="3">
-        <v>0</v>
+      <c r="F907" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G907" s="3" t="s">
         <v>1617</v>
@@ -28107,8 +28107,8 @@
       <c r="E973" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F973" s="3">
-        <v>0</v>
+      <c r="F973" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G973" s="3" t="s">
         <v>1615</v>
@@ -29119,8 +29119,8 @@
       <c r="E1017" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1017" s="3">
-        <v>0</v>
+      <c r="F1017" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1017" s="3" t="s">
         <v>1616</v>
@@ -29280,8 +29280,8 @@
       <c r="E1024" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1024" s="3">
-        <v>0</v>
+      <c r="F1024" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1024" s="3" t="s">
         <v>1617</v>
@@ -29832,8 +29832,8 @@
       <c r="E1048" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1048" s="3">
-        <v>0</v>
+      <c r="F1048" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1048" s="3" t="s">
         <v>1615</v>
@@ -30039,8 +30039,8 @@
       <c r="E1057" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1057" s="3">
-        <v>0</v>
+      <c r="F1057" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1057" s="3" t="s">
         <v>1615</v>
@@ -30407,8 +30407,8 @@
       <c r="E1073" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1073" s="3">
-        <v>0</v>
+      <c r="F1073" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1073" s="3" t="s">
         <v>1615</v>
@@ -31856,8 +31856,8 @@
       <c r="E1136" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1136" s="3">
-        <v>0</v>
+      <c r="F1136" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1136" s="3" t="s">
         <v>1616</v>
@@ -32247,8 +32247,8 @@
       <c r="E1153" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1153" s="3">
-        <v>0</v>
+      <c r="F1153" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1153" s="3" t="s">
         <v>1615</v>
@@ -32339,8 +32339,8 @@
       <c r="E1157" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1157" s="3">
-        <v>0</v>
+      <c r="F1157" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1157" s="3" t="s">
         <v>1615</v>
@@ -32615,8 +32615,8 @@
       <c r="E1169" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1169" s="3">
-        <v>0</v>
+      <c r="F1169" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1169" s="3" t="s">
         <v>1615</v>
@@ -33236,8 +33236,8 @@
       <c r="E1196" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1196" s="3">
-        <v>0</v>
+      <c r="F1196" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1196" s="3" t="s">
         <v>1615</v>
@@ -34156,8 +34156,8 @@
       <c r="E1236" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1236" s="3">
-        <v>0</v>
+      <c r="F1236" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1236" s="3" t="s">
         <v>1615</v>
@@ -35651,8 +35651,8 @@
       <c r="E1301" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1301" s="3">
-        <v>0</v>
+      <c r="F1301" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1301" s="3" t="s">
         <v>1615</v>
@@ -35973,8 +35973,8 @@
       <c r="E1315" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1315" s="3">
-        <v>0</v>
+      <c r="F1315" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1315" s="3" t="s">
         <v>1615</v>
@@ -37974,8 +37974,8 @@
       <c r="E1402" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1402" s="3">
-        <v>0</v>
+      <c r="F1402" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1402" s="3" t="s">
         <v>1615</v>
@@ -38618,8 +38618,8 @@
       <c r="E1430" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1430" s="3">
-        <v>0</v>
+      <c r="F1430" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1430" s="3" t="s">
         <v>1616</v>
@@ -39354,8 +39354,8 @@
       <c r="E1462" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1462" s="3">
-        <v>0</v>
+      <c r="F1462" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1462" s="3" t="s">
         <v>1615</v>
@@ -39377,8 +39377,8 @@
       <c r="E1463" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1463" s="3">
-        <v>0</v>
+      <c r="F1463" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1463" s="3" t="s">
         <v>1615</v>
@@ -39446,8 +39446,8 @@
       <c r="E1466" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1466" s="3">
-        <v>0</v>
+      <c r="F1466" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1466" s="3" t="s">
         <v>1615</v>
@@ -40159,8 +40159,8 @@
       <c r="E1497" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F1497" s="3">
-        <v>0</v>
+      <c r="F1497" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="G1497" s="3" t="s">
         <v>1615</v>

--- a/data/roles_areas.xlsx
+++ b/data/roles_areas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Inventario\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7C71D2-7A20-4D8B-A5EF-C0EBBBB48A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEEFF3D-C53A-4C65-86F4-0A7A05BC7F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F2D9A4D-AB14-4069-820F-8029A79ED844}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15360" uniqueCount="1634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15354" uniqueCount="1631">
   <si>
     <t>Nombre</t>
   </si>
@@ -4931,15 +4931,6 @@
   </si>
   <si>
     <t>Column4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evelyn Peña </t>
-  </si>
-  <si>
-    <t>Esclava</t>
-  </si>
-  <si>
-    <t>Todo el dia</t>
   </si>
 </sst>
 </file>
@@ -5373,8 +5364,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D2C8E0AA-CC08-447B-95CB-DF9A6B78DCD0}" name="Table2" displayName="Table2" ref="A1:G1539" totalsRowShown="0" dataDxfId="16">
-  <autoFilter ref="A1:G1539" xr:uid="{D2C8E0AA-CC08-447B-95CB-DF9A6B78DCD0}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D2C8E0AA-CC08-447B-95CB-DF9A6B78DCD0}" name="Table2" displayName="Table2" ref="A1:G1538" totalsRowShown="0" dataDxfId="16">
+  <autoFilter ref="A1:G1538" xr:uid="{D2C8E0AA-CC08-447B-95CB-DF9A6B78DCD0}">
     <filterColumn colId="6">
       <filters>
         <filter val="0"/>
@@ -5741,7 +5732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EE56F94-5C7B-4804-99D1-BF13AFA71C59}">
-  <dimension ref="A1:G1539"/>
+  <dimension ref="A1:G1538"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -41124,29 +41115,6 @@
       </c>
       <c r="G1538" s="3" t="s">
         <v>1614</v>
-      </c>
-    </row>
-    <row r="1539" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1539" s="2">
-        <v>23428</v>
-      </c>
-      <c r="B1539" s="2" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C1539" s="3" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D1539" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1539" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1539" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1539" s="3" t="s">
-        <v>1633</v>
       </c>
     </row>
   </sheetData>

--- a/data/roles_areas.xlsx
+++ b/data/roles_areas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Inventario\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2193D9E2-76DE-42D6-ACC2-12B20FCC048C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6FB150-3BDF-4CBB-928D-4210C2988AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F2D9A4D-AB14-4069-820F-8029A79ED844}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16913" uniqueCount="1635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16914" uniqueCount="1635">
   <si>
     <t>Nombre</t>
   </si>
@@ -5054,7 +5054,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
+        <sz val="8"/>
         <color auto="1"/>
         <name val="Arial Narrow"/>
         <family val="2"/>
@@ -5198,7 +5198,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="8"/>
+        <sz val="9"/>
         <color auto="1"/>
         <name val="Arial Narrow"/>
         <family val="2"/>
@@ -5393,16 +5393,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{461D300D-52A9-40EF-8E94-267B307E0A23}" name="Table3" displayName="Table3" ref="A1:G1540" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{461D300D-52A9-40EF-8E94-267B307E0A23}" name="Table3" displayName="Table3" ref="A1:G1540" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="A1:G1540" xr:uid="{461D300D-52A9-40EF-8E94-267B307E0A23}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{DE5222DA-8310-4C9E-95BB-D67CA4E25CD0}" name="Número" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{C58F199E-856D-453B-8CCA-CB6C740C8301}" name="Nombre" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{450E7281-F21C-4A3C-83D7-282C258A2897}" name="Activity" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{8AEFA17A-519A-4477-B87A-A12757A14894}" name="Location " dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{0F5E1E81-5CA3-4FF6-AF8C-5C6E06324A06}" name="Oracle Location" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{7F7A3F91-53EE-4568-833A-2AF449BB399D}" name="SVG_ID" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{EEF31983-DD98-4B4C-A1D2-F9580420D51E}" name="Shift" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{DE5222DA-8310-4C9E-95BB-D67CA4E25CD0}" name="Número" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{C58F199E-856D-453B-8CCA-CB6C740C8301}" name="Nombre" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{450E7281-F21C-4A3C-83D7-282C258A2897}" name="Activity" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{8AEFA17A-519A-4477-B87A-A12757A14894}" name="Location " dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{0F5E1E81-5CA3-4FF6-AF8C-5C6E06324A06}" name="Oracle Location" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{7F7A3F91-53EE-4568-833A-2AF449BB399D}" name="SVG_ID" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{EEF31983-DD98-4B4C-A1D2-F9580420D51E}" name="Shift" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -41113,7 +41113,9 @@
       <c r="E1540" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F1540" s="2"/>
+      <c r="F1540" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="G1540" s="2" t="s">
         <v>1610</v>
       </c>
@@ -78411,6 +78413,10 @@
       <c r="E1540" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="F1540" s="5" t="str">
+        <f>_xlfn.XLOOKUP(D1540, Table1[Location], Table1[SVG Location], 0,0)</f>
+        <v>Warehouse</v>
+      </c>
       <c r="G1540" s="5" t="s">
         <v>1610</v>
       </c>

--- a/data/roles_areas.xlsx
+++ b/data/roles_areas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Inventario\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CF768D-F8B6-485B-B09A-11DAADBCDDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A0B2D2-B5E2-4829-A243-564C3AD6EFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8F2D9A4D-AB14-4069-820F-8029A79ED844}"/>
   </bookViews>
@@ -5051,7 +5051,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -5070,6 +5069,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -5386,18 +5386,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6BFDA3D1-E0DF-4D39-A85B-B5339DDF4CA1}" name="Table3" displayName="Table3" ref="A1:G1539" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6BFDA3D1-E0DF-4D39-A85B-B5339DDF4CA1}" name="Table3" displayName="Table3" ref="A1:G1539" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="A1:G1539" xr:uid="{6BFDA3D1-E0DF-4D39-A85B-B5339DDF4CA1}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{09F1E51A-87DD-4CEF-B359-AA9C6D4CF7F8}" name="Número" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{BD6EF637-CBCA-4B3C-9142-69914F2B8026}" name="Nombre" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{6235C8A0-09E3-4226-B4C8-73901B18FF19}" name="Activity" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{7E493D69-0506-4483-92EA-53D474C4795B}" name="Location " dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{18C8C368-E524-47C2-9E79-85D68FAEF9E5}" name="Oracle Location" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{68EB4D1B-18EE-4B38-8BD0-B9BD685B0C57}" name="SVG Location" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{09F1E51A-87DD-4CEF-B359-AA9C6D4CF7F8}" name="Número" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{BD6EF637-CBCA-4B3C-9142-69914F2B8026}" name="Nombre" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{6235C8A0-09E3-4226-B4C8-73901B18FF19}" name="Activity" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{7E493D69-0506-4483-92EA-53D474C4795B}" name="Location " dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{18C8C368-E524-47C2-9E79-85D68FAEF9E5}" name="Oracle Location" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{68EB4D1B-18EE-4B38-8BD0-B9BD685B0C57}" name="SVG Location" dataDxfId="1">
       <calculatedColumnFormula>_xlfn.XLOOKUP(Table3[[#This Row],[Location ]], Table1[Location],Table1[SVG Location],0,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{FC69C084-0E13-4D02-97EF-2D7D6FA9141F}" name="Shift" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{FC69C084-0E13-4D02-97EF-2D7D6FA9141F}" name="Shift" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/data/roles_areas.xlsx
+++ b/data/roles_areas.xlsx
@@ -54074,7 +54074,7 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>EVLEYN PENA</t>
+          <t>EVELYN PENA</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr">

--- a/data/roles_areas.xlsx
+++ b/data/roles_areas.xlsx
@@ -490,11 +490,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>14620</v>
+        <v>22581</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CALZADILLAS MARQUEZ, MIGUEL ALONSO</t>
+          <t>DE LA CRUZ DAVILA, NORMA ARACELI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turno 2 / 6PM- 6AM</t>
+          <t>Turno 1 / 6AM- 6PM</t>
         </is>
       </c>
     </row>
@@ -805,11 +805,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>22581</v>
+        <v>14650</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DE LA CRUZ DAVILA, NORMA ARACELI</t>
+          <t>DIAZ CARRILLO, ANETTE DAYANA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2240,11 +2240,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>18162</v>
+        <v>17292</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ANDRADE RODRIGUEZ, JAZMIN LISSETE</t>
+          <t>DE LOS SANTOS CHAVEZ, MERCEDES</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Turno 2 / 6PM- 6AM</t>
+          <t>Turno 1 / 6AM- 6PM</t>
         </is>
       </c>
     </row>
@@ -2835,11 +2835,11 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>22028</v>
+        <v>21097</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ARENAS BARRERA, JUAN LUIS</t>
+          <t>DE LA PAZ MONROY, SANDRA ANAID</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PLANTA</t>
+          <t>MONKITS / MONXDU100 / MONXDU(1350)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6990,11 +6990,11 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>14675</v>
+        <v>21578</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CASTILLO PEREZ, LEOPOLDO</t>
+          <t>DE LA PEÑA PLATA, MARIANA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>PLANTA</t>
+          <t>MONEP / MONSM</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -10346,11 +10346,11 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>14650</v>
+        <v>17691</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DIAZ CARRILLO, ANETTE DAYANA</t>
+          <t>PEREZ LARA, MAGDIEL</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10661,11 +10661,11 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>21097</v>
+        <v>20222</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>DE LA PAZ MONROY, SANDRA ANAID</t>
+          <t>DIAZ CARRILLO, PAOLA VERONICA</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10675,17 +10675,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>PLANTA</t>
+          <t>SHIP / AFC</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>MTY 1</t>
+          <t>SHIP</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -10696,11 +10696,11 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>21578</v>
+        <v>19522</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>DE LA PEÑA PLATA, MARIANA</t>
+          <t>HERNANDEZ REYNA, CRISTIAN ITZEL</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10710,17 +10710,12 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>PLANTA</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>MTY 1</t>
+          <t>MONDP L1, L2. MONMC / MONSKID</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -11081,16 +11076,16 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>17292</v>
+        <v>14913</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>DE LOS SANTOS CHAVEZ, MERCEDES</t>
+          <t>EGGENBERGER CARPIO, GEORG GERD</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Control table / capturista</t>
+          <t>Control Table Leader</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -11711,11 +11706,11 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>17691</v>
+        <v>14661</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PEREZ LARA, MAGDIEL</t>
+          <t>VARGAS GRIJALVA, JAQUELINE</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -11746,11 +11741,11 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>20222</v>
+        <v>23016</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>DIAZ CARRILLO, PAOLA VERONICA</t>
+          <t>JARAMILLO DAVILA, PERLA GUADALUPE</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -11760,7 +11755,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Ship</t>
+          <t>MONBLW / MONCR</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -11770,7 +11765,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>SHIP</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -12691,16 +12686,16 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>14913</v>
+        <v>18949</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>EGGENBERGER CARPIO, GEORG GERD</t>
+          <t>VELA ROMO, ANGELES ARACELY</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Control Table Leader</t>
+          <t>Control Table</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -15841,36 +15836,31 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>15626</v>
+        <v>19079</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>GARCIA ALMAGUER, JULIAN TADEO</t>
+          <t>MARTINEZ PERCHES, KATIA LISSET</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Control Table Leader</t>
+          <t>Control Table</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>PLANTA</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>MTY 1</t>
+          <t>MONCOILS / MONPRE</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Turno 2 / 6PM- 6AM</t>
+          <t>Turno 1 / 6AM- 6PM</t>
         </is>
       </c>
     </row>
@@ -16983,7 +16973,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Turno 2 / 6PM- 6AM</t>
+          <t>Turno 1 / 6AM- 6PM</t>
         </is>
       </c>
     </row>
@@ -24887,11 +24877,11 @@
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>19522</v>
+        <v>18935</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>HERNANDEZ REYNA, CRISTIAN ITZEL</t>
+          <t>POPOCA VILLARREAL, DANIEL</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -24901,12 +24891,17 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>PLANTA</t>
+          <t>MTY1 / FASTENAL</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>MTY 1</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -26072,11 +26067,11 @@
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>14898</v>
+        <v>21098</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>IRACHETA GAMEZ, MOISES NEFTALI</t>
+          <t>QUIRARTE ROMO, ANDREA</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -26086,17 +26081,22 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>PLANTA</t>
+          <t>BLANKED TAGS</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>MTY 1</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>Turno 2 / 6PM- 6AM</t>
+          <t>Turno 1 / 6AM- 6PM</t>
         </is>
       </c>
     </row>
@@ -26242,31 +26242,31 @@
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>23016</v>
+        <v>20250</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>JARAMILLO DAVILA, PERLA GUADALUPE</t>
+          <t>MORLET OSUNA, ELSIE ASTRID</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Control Table</t>
+          <t>Control table / capturista</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>Ship</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>SHIP</t>
+          <t>MTY 1</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>SHIP</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -28022,16 +28022,16 @@
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>14661</v>
+        <v>23702</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>VARGAS GRIJALVA, JAQUELINE</t>
+          <t>CELIA DANIELA ZAMORES BENAVIDES</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Control Table</t>
+          <t>Control table / capturista</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
@@ -32215,11 +32215,11 @@
     </row>
     <row r="911">
       <c r="A911" t="n">
-        <v>19079</v>
+        <v>14548</v>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>MARTINEZ PERCHES, KATIA LISSET</t>
+          <t>RUIZ DIAZ, KENIA THALI</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -32229,12 +32229,17 @@
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>Laredo</t>
+          <t>MONXDM / MONDA</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>MTY 1</t>
         </is>
       </c>
       <c r="F911" t="inlineStr">
         <is>
-          <t>Laredo</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G911" t="inlineStr">
@@ -33748,16 +33753,16 @@
     </row>
     <row r="955">
       <c r="A955" t="n">
-        <v>18949</v>
+        <v>23667</v>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>VELA ROMO, ANGELES ARACELY</t>
+          <t>REGINA PAMELA VELA GONZALEZ</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Control Table</t>
+          <t>Control table / capturista</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -36571,21 +36576,21 @@
     </row>
     <row r="1036">
       <c r="A1036" t="n">
-        <v>20250</v>
+        <v>20841</v>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>MORLET OSUNA, ELSIE ASTRID</t>
+          <t>YEPIZ JARA, ABDIEL</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Control table / capturista</t>
+          <t>Control Table</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>PIPING / PROTOTIPOS / MRB</t>
         </is>
       </c>
       <c r="E1036" t="inlineStr">
@@ -36595,7 +36600,7 @@
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G1036" t="inlineStr">
@@ -36606,11 +36611,11 @@
     </row>
     <row r="1037">
       <c r="A1037" t="n">
-        <v>22354</v>
+        <v>14620</v>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>AGUILAR QUIROGA, JORGE LUIS</t>
+          <t>CALZADILLAS MARQUEZ, MIGUEL ALONSO</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
@@ -36956,11 +36961,11 @@
     </row>
     <row r="1047">
       <c r="A1047" t="n">
-        <v>18935</v>
+        <v>14898</v>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>POPOCA VILLARREAL, DANIEL</t>
+          <t>IRACHETA GAMEZ, MOISES NEFTALI</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
@@ -36970,22 +36975,22 @@
       </c>
       <c r="D1047" t="inlineStr">
         <is>
-          <t>PLANTA</t>
+          <t>MONCOILS / MONPRE / MTY1 / FASTENAL</t>
         </is>
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t>MTY 1</t>
+          <t>MTY1</t>
         </is>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G1047" t="inlineStr">
         <is>
-          <t>Turno 1 / 6AM- 6PM</t>
+          <t>Turno 2 / 6PM- 6AM</t>
         </is>
       </c>
     </row>
@@ -39476,16 +39481,16 @@
     </row>
     <row r="1119">
       <c r="A1119" t="n">
-        <v>15490</v>
+        <v>18162</v>
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>LOPEZ CANTU, ALAN HUMBERTO</t>
+          <t>ANDRADE RODRIGUEZ, JAZMIN LISSETE</t>
         </is>
       </c>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>Control Table</t>
+          <t>Control table / capturista</t>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
@@ -39505,7 +39510,7 @@
       </c>
       <c r="G1119" t="inlineStr">
         <is>
-          <t>Turno 2 / 6PM- 6AM</t>
+          <t>Turno 1 / 6AM- 6PM</t>
         </is>
       </c>
     </row>
@@ -39861,11 +39866,11 @@
     </row>
     <row r="1130">
       <c r="A1130" t="n">
-        <v>21188</v>
+        <v>22354</v>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>MELENDEZ ORDAZ, DOMINGO ARTURO</t>
+          <t>AGUILAR QUIROGA, JORGE LUIS</t>
         </is>
       </c>
       <c r="C1130" t="inlineStr">
@@ -40701,11 +40706,11 @@
     </row>
     <row r="1154">
       <c r="A1154" t="n">
-        <v>21098</v>
+        <v>22244</v>
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>QUIRARTE ROMO, ANDREA</t>
+          <t>RAYGOZA SANTANA, JUAN ENRIQUE</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
@@ -40715,22 +40720,22 @@
       </c>
       <c r="D1154" t="inlineStr">
         <is>
-          <t>PLANTA</t>
+          <t>MONXDM / MONDA / PIPING / PROTOTIPOS / MRB</t>
         </is>
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t>MTY 1</t>
+          <t>SHIP</t>
         </is>
       </c>
       <c r="F1154" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G1154" t="inlineStr">
         <is>
-          <t>Turno 1 / 6AM- 6PM</t>
+          <t>Turno 2 / 6PM- 6AM</t>
         </is>
       </c>
     </row>
@@ -41261,11 +41266,11 @@
     </row>
     <row r="1170">
       <c r="A1170" t="n">
-        <v>14548</v>
+        <v>22356</v>
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>RUIZ DIAZ, KENIA THALI</t>
+          <t>MURGUIA ARREOLA, ALEJANDRA</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
@@ -41275,7 +41280,7 @@
       </c>
       <c r="D1170" t="inlineStr">
         <is>
-          <t>PLANTA</t>
+          <t>MONBLW / MONCR / BLANKED TAGS</t>
         </is>
       </c>
       <c r="E1170" t="inlineStr">
@@ -41285,12 +41290,12 @@
       </c>
       <c r="F1170" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G1170" t="inlineStr">
         <is>
-          <t>Turno 1 / 6AM- 6PM</t>
+          <t>Turno 2 / 6PM- 6AM</t>
         </is>
       </c>
     </row>
@@ -42826,36 +42831,36 @@
     </row>
     <row r="1215">
       <c r="A1215" t="n">
-        <v>22244</v>
+        <v>23479</v>
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>RAYGOZA SANTANA, JUAN ENRIQUE</t>
+          <t>LAURA YARESSI TREVINO NAVEJAR</t>
         </is>
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Control Table</t>
+          <t>Control table / capturista</t>
         </is>
       </c>
       <c r="D1215" t="inlineStr">
         <is>
-          <t>Ship</t>
+          <t>PLANTA</t>
         </is>
       </c>
       <c r="E1215" t="inlineStr">
         <is>
-          <t>SHIP</t>
+          <t>MTY 1</t>
         </is>
       </c>
       <c r="F1215" t="inlineStr">
         <is>
-          <t>SHIP</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G1215" t="inlineStr">
         <is>
-          <t>Turno 2 / 6PM- 6AM</t>
+          <t>Turno 1 / 6AM- 6PM</t>
         </is>
       </c>
     </row>
@@ -45729,16 +45734,16 @@
     </row>
     <row r="1298">
       <c r="A1298" t="n">
-        <v>18735</v>
+        <v>15626</v>
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>SOTO BALANDRAN, JOSE LUIS</t>
+          <t>GARCIA ALMAGUER, JULIAN TADEO</t>
         </is>
       </c>
       <c r="C1298" t="inlineStr">
         <is>
-          <t>Control Table</t>
+          <t>Control Table Leader</t>
         </is>
       </c>
       <c r="D1298" t="inlineStr">
@@ -45758,7 +45763,7 @@
       </c>
       <c r="G1298" t="inlineStr">
         <is>
-          <t>Turno 1 / 6AM- 6PM</t>
+          <t>Turno 2 / 6PM- 6AM</t>
         </is>
       </c>
     </row>
@@ -47549,21 +47554,21 @@
     </row>
     <row r="1350">
       <c r="A1350" t="n">
-        <v>21353</v>
+        <v>14737</v>
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>SANCHEZ RODRIGUEZ, ERNESTO GABRIEL</t>
+          <t>VALENZUELA OROZCO, LUIS ADRIAN</t>
         </is>
       </c>
       <c r="C1350" t="inlineStr">
         <is>
-          <t>Control table / capturista</t>
+          <t>Control Table</t>
         </is>
       </c>
       <c r="D1350" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>MONKITS / MONXDU100 / MONXDU(1350) / MONEP / MONSM</t>
         </is>
       </c>
       <c r="E1350" t="inlineStr">
@@ -47573,7 +47578,7 @@
       </c>
       <c r="F1350" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G1350" t="inlineStr">
@@ -47689,16 +47694,16 @@
     </row>
     <row r="1354">
       <c r="A1354" t="n">
-        <v>14866</v>
+        <v>15490</v>
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>SANCHEZ VAZQUEZ, ALAN ABIUD</t>
+          <t>LOPEZ CANTU, ALAN HUMBERTO</t>
         </is>
       </c>
       <c r="C1354" t="inlineStr">
         <is>
-          <t>Control table / capturista</t>
+          <t>Control Table</t>
         </is>
       </c>
       <c r="D1354" t="inlineStr">
@@ -49194,11 +49199,11 @@
     </row>
     <row r="1397">
       <c r="A1397" t="n">
-        <v>20841</v>
+        <v>15334</v>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>YEPIZ JARA, ABDIEL</t>
+          <t>ZARCO GUTIERREZ, SILVIA YARELI</t>
         </is>
       </c>
       <c r="C1397" t="inlineStr">
@@ -49208,7 +49213,7 @@
       </c>
       <c r="D1397" t="inlineStr">
         <is>
-          <t>PLANTA</t>
+          <t>SHIP / AFC / MONDP L1, L2. MONMC / MONSKID</t>
         </is>
       </c>
       <c r="E1397" t="inlineStr">
@@ -49218,12 +49223,12 @@
       </c>
       <c r="F1397" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G1397" t="inlineStr">
         <is>
-          <t>Turno 1 / 6AM- 6PM</t>
+          <t>Turno 2 / 6PM- 6AM</t>
         </is>
       </c>
     </row>
@@ -49609,11 +49614,11 @@
     </row>
     <row r="1409">
       <c r="A1409" t="n">
-        <v>15074</v>
+        <v>21353</v>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>TERAN LEAL, RAFAEL</t>
+          <t>SANCHEZ RODRIGUEZ, ERNESTO GABRIEL</t>
         </is>
       </c>
       <c r="C1409" t="inlineStr">
@@ -50509,21 +50514,21 @@
     </row>
     <row r="1435">
       <c r="A1435" t="n">
-        <v>22356</v>
+        <v>15074</v>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>MURGUIA ARREOLA, ALEJANDRA</t>
+          <t>TERAN LEAL, RAFAEL</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Control Table</t>
+          <t>Control table / capturista</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr">
         <is>
-          <t>PLANTA</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E1435" t="inlineStr">
@@ -50959,11 +50964,11 @@
     </row>
     <row r="1448">
       <c r="A1448" t="n">
-        <v>21180</v>
+        <v>21188</v>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>TREVIÑO GRANADOS, VICTOR MANUEL</t>
+          <t>MELENDEZ ORDAZ, DOMINGO ARTURO</t>
         </is>
       </c>
       <c r="C1448" t="inlineStr">
@@ -51204,16 +51209,16 @@
     </row>
     <row r="1455">
       <c r="A1455" t="n">
-        <v>21132</v>
+        <v>14866</v>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>MULLER GARCIA, EDGAR</t>
+          <t>SANCHEZ VAZQUEZ, ALAN ABIUD</t>
         </is>
       </c>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>Control Table</t>
+          <t>Control table / capturista</t>
         </is>
       </c>
       <c r="D1455" t="inlineStr">
@@ -52077,11 +52082,11 @@
     </row>
     <row r="1480">
       <c r="A1480" t="n">
-        <v>20808</v>
+        <v>21180</v>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>PEREDA PEREZ, AXEL IVAN</t>
+          <t>TREVIÑO GRANADOS, VICTOR MANUEL</t>
         </is>
       </c>
       <c r="C1480" t="inlineStr">
@@ -53407,11 +53412,11 @@
     </row>
     <row r="1518">
       <c r="A1518" t="n">
-        <v>14737</v>
+        <v>22028</v>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>VALENZUELA OROZCO, LUIS ADRIAN</t>
+          <t>ARENAS BARRERA, JUAN LUIS</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr">
@@ -53436,7 +53441,7 @@
       </c>
       <c r="G1518" t="inlineStr">
         <is>
-          <t>Turno 2 / 6PM- 6AM</t>
+          <t>Turno 1 / 6AM- 6PM</t>
         </is>
       </c>
     </row>
@@ -53547,11 +53552,11 @@
     </row>
     <row r="1522">
       <c r="A1522" t="n">
-        <v>15334</v>
+        <v>14675</v>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>ZARCO GUTIERREZ, SILVIA YARELI</t>
+          <t>CASTILLO PEREZ, LEOPOLDO</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr">
@@ -53576,7 +53581,7 @@
       </c>
       <c r="G1522" t="inlineStr">
         <is>
-          <t>Turno 2 / 6PM- 6AM</t>
+          <t>Turno 1 / 6AM- 6PM</t>
         </is>
       </c>
     </row>
@@ -53792,16 +53797,16 @@
     </row>
     <row r="1529">
       <c r="A1529" t="n">
-        <v>23479</v>
+        <v>18735</v>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>LAURA YARESSI TREVINO NAVEJAR</t>
+          <t>SOTO BALANDRAN, JOSE LUIS</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr">
         <is>
-          <t>Control table / capturista</t>
+          <t>Control Table</t>
         </is>
       </c>
       <c r="D1529" t="inlineStr">
@@ -54176,19 +54181,32 @@
       </c>
     </row>
     <row r="1540">
+      <c r="A1540" t="n">
+        <v>21132</v>
+      </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>Buyer 1</t>
+          <t>MULLER GARCIA, EDGAR</t>
         </is>
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>Control table / capturista</t>
+          <t>Control Table</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>3PL</t>
+        </is>
+      </c>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>MTY3</t>
         </is>
       </c>
       <c r="F1540" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MTY3</t>
         </is>
       </c>
       <c r="G1540" t="inlineStr">
@@ -54198,31 +54216,44 @@
       </c>
     </row>
     <row r="1541">
+      <c r="A1541" t="n">
+        <v>20808</v>
+      </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>Buyer 2</t>
+          <t>PEREDA PEREZ, AXEL IVAN</t>
         </is>
       </c>
       <c r="C1541" t="inlineStr">
         <is>
-          <t>Control table / capturista</t>
+          <t>Control Table</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>3PL</t>
+        </is>
+      </c>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>MTY3</t>
         </is>
       </c>
       <c r="F1541" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MTY3</t>
         </is>
       </c>
       <c r="G1541" t="inlineStr">
         <is>
-          <t>Turno 1 / 6AM- 6PM</t>
+          <t>Turno 2 / 6PM- 6AM</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="B1542" t="inlineStr">
         <is>
-          <t>Buyer 3</t>
+          <t>Buyer 1</t>
         </is>
       </c>
       <c r="C1542" t="inlineStr">
@@ -54230,14 +54261,24 @@
           <t>Control table / capturista</t>
         </is>
       </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>3PL</t>
+        </is>
+      </c>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>MTY3</t>
+        </is>
+      </c>
       <c r="F1542" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MTY3</t>
         </is>
       </c>
       <c r="G1542" t="inlineStr">
         <is>
-          <t>Turno 1 / 6AM- 6PM</t>
+          <t>Turno 2 / 6PM- 6AM</t>
         </is>
       </c>
     </row>
